--- a/data_extactor/batch_10_fa/batch_0090_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0090_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | مانیتورینگ | تفکر انتقادی | ریاضیات | گوش دادن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | ریاضیات | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | طراحی | مهندسی و فناوری | مکانیک | ساختمان و ساخت‌وساز | مدیریت و امور اداری | تولید و فرآوری | خدمات مشتریان و پرسنل</t>
+          <t>ریاضیات | طراحی | مهندسی و فناوری | مکانیک | ساختمان و ساخت‌وساز | مدیریت و اداره | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چالاکی دست | دقت کنترل | ثبات بازو-دست | بینایی نزدیک | زمان عکس‌العمل | چالاکی انگشتان | سازماندهی اطلاعات | تجسم | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مشکلات | درک شفاهی | سرعت ادراکی | استدلال ریاضی | بیان شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | درک عمق | قدرت تنه</t>
+          <t>مهارت دستی | دقت کنترل | ثبات دست و بازو | بینایی نزدیک | زمان عکس‌العمل | مهارت انگشتان | ترتیب‌دهی اطلاعات | تجسم | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | سرعت ادراکی | استدلال ریاضی | بیان شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | درک عمق | قدرت تنه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | اهمیت تکرار وظایف یکسان | ایمیل | مکالمات تلفنی | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران | داخل ساختمان، بدون کنترل شرایط محیطی</t>
+          <t>اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | ایمیل | مکالمات تلفنی | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | کابینت‌سازان و نجاران نیمکت | نجاران | حکاکان و تیزاب‌کاران | الگوسازان پارچه و پوشاک | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | کارگران پرداخت و سایش دستی | کارگران نشانه‌گذاری فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | ورق‌کاران فلزی | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | ابزارسازان و قالب‌سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | کابینت‌سازان و نجاران نیمکت | نجّاران | حکاکان و تیزاب‌کاران | الگوسازان پارچه و پوشاک | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | کارگران ورق‌کاری | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار خودکار انبارداری | نرم‌افزار کنترل عددی کامپیوتری CNC | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word</t>
+          <t>Adobe Acrobat | نرم‌افزار خودکار موجودی | نرم‌افزار کنترل عددی کامپیوتری CNC | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی</t>
+          <t>نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | بینایی نزدیک | چالاکی دست | ثبات بازو-دست | کنترل سرعت | زمان عکس‌العمل | حساسیت به مشکلات | چالاکی انگشتان | استقامت | قدرت تنه | هماهنگی چند عضو | توجه انتخابی | درک عمق | بینایی دور | قدرت ایستا | استدلال استقرایی | استدلال قیاسی</t>
+          <t>دقت کنترل | بینایی نزدیک | مهارت دستی | ثبات دست و بازو | کنترل نرخ | زمان عکس‌العمل | حساسیت به مسئله | مهارت انگشتان | استقامت | قدرت تنه | هماهنگی چند عضو | توجه انتخابی | درک عمق | بینایی دور | قدرت ایستا | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | اهمیت دقیق یا درست بودن | داخل ساختمان، بدون کنترل شرایط محیطی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارگران | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سایش و پرداخت | برش‌دهندگان و هرس‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مته و سوراخ‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آهنگری فلز و پلاستیک | کارگران پرداخت و سایش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سایش، لپینگ، پرداخت و بافینگ فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تراش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌های کفش‌دوزی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تیزکنندگان و سوهان‌کاران ابزار | ابزارسازان و قالب‌سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی</t>
+          <t>تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AS/400 Database | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple macOS | Autodesk AutoCAD | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار کنترل عددی کامپیوتری CNC | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار کنترل موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Oracle Java | نرم‌افزار ثبت زمان | Vero Software ALPHACAM | YouTube</t>
+          <t>AS/400 Database | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple macOS | Autodesk AutoCAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار کنترل عددی کامپیوتری CNC | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار کنترل موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Oracle Java | نرم‌افزار ثبت زمان | Vero Software ALPHACAM | YouTube</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن‌گفتن | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | زمان عکس‌العمل | دقت کنترل | چالاکی دست | درک شفاهی | حساسیت به مشکلات | هماهنگی چند عضو | قدرت ایستا | قدرت تنه | توجه شنوایی | بینایی دور | چالاکی انگشتان | ثبات بازو-دست | توجه انتخابی | تجسم | سرعت ادراکی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | سازماندهی اطلاعات | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری بدنی | قدرت پویا | کنترل سرعت | انعطاف‌پذیری در بستن فضا</t>
+          <t>بینایی نزدیک | زمان عکس‌العمل | دقت کنترل | مهارت دستی | درک شفاهی | حساسیت به مسئله | هماهنگی چند عضو | قدرت ایستا | قدرت تنه | توجه شنیداری | بینایی دور | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | تجسم | سرعت ادراکی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت پویا | کنترل نرخ | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض آلاینده‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان به صورت ایستاده | داخل ساختمان، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سایش و پرداخت | برش‌دهندگان و هرس‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش, پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مته و سوراخ‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آهنگری فلز و پلاستیک | کارگران پرداخت و سایش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سایش، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تراش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | اپراتورها و متصدیان ماشین‌های کفش‌دوزی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تیزکنندگان و سوهان‌کاران ابزار | ابزارسازان و قالب‌سازان</t>
+          <t>تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل نظارتی و گردآوری داده‌ها SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP | Autodesk AutoCAD</t>
+          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP | Autodesk AutoCAD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات بازو-دست | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان عکس‌العمل | حساسیت به مشکلات | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>داخل ساختمان، بدون کنترل شرایط محیطی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | پیامد خطا | درجه خودکارسازی | اهمیت تکرار وظایف یکسان | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران نیمکت | پرداخت‌کاران مبلمان | مدل‌سازان چوب | الگوسازان چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی | نجاران | دستیاران نجار | رویه‌کوبان | سنباده‌زنان و پرداخت‌کاران کف | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | بازرسان، تست‌کنندگان، دسته‌بندها، نمونه‌برداران و توزیع‌کنندگان | اپراتورهای ابزار کنترل عددی کامپیوتری | سرپرستان خط اول کارگران تولیدی و عملیاتی | دستیاران کارگران تولیدی | کارگران تولیدی، سایر موارد | درجه‌بندان و ارزیابان گرده‌بینه | اپراتورها و متصدیان ماشین‌های اتصال چسبی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک</t>
+          <t>کابینت‌سازان و نجاران نیمکت | پرداخت‌کاران مبلمان | مدل‌سازان چوب | الگوسازان چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی | نجّاران | دستیاران--نجاران | روکوبان | سنباده‌کاران و پرداخت‌کاران کف | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | اپراتورهای ابزار کنترل عددی کامپیوتری | سرپرستان رده اول کارگران تولید و بهره‌برداری | کمک‌کاران--کارگران تولید | کارگران تولید، سایر موارد | درجه‌بندی‌کنندگان و ارزیابان چوب | اپراتورها و متصدیان ماشین‌های اتصال چسبی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | مانیتورینگ | گوش دادن فعال | تفکر انتقادی | نگارش | سخن‌گفتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فیزیک | مکانیک | امنیت و ایمنی عمومی | ریاضیات | مهندسی و فناوری | شیمی | طراحی</t>
+          <t>فیزیک | مکانیک | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | شیمی | طراحی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | درک شفاهی | درک کتبی | بیان شفاهی | سازماندهی اطلاعات | سرعت ادراکی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | بیان کتبی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری در بستن فضا | تشخیص گفتار | بینایی دور | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | خلاقیت | روان بودن ایده‌ها | اشتراک زمانی | توجه شنوایی | حساسیت شنوایی | تشخیص رنگ بصری</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | بیان کتبی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار | بینایی دور | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | اصالت | روانی ایده‌ها | تقسیم توجه | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، کنترل شرایط محیطی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | ارتباط با دیگران | پیامد خطا | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارگران | نزدیکی فیزیکی | قرار گرفتن در معرض تابش | صرف زمان به صورت نشسته</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | ارتباط با دیگران | پیامد خطا | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | قرار گرفتن در معرض تابش | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه قدرت زیست‌توده | مهندسان شیمی | اپراتورهای سیستم و نیروگاه شیمیایی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران الکتریکی و الکترونیکی نیروگاه، پست برق و رله | اپراتورهای نیروگاه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان هسته‌ای | تکنسین‌های مانیتورینگ هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | اپراتورهای کارخانه و سامانه‌های شیمیایی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان هسته‌ای | تکنسین‌های نظارت هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ABB MicroSCADA Pro DMS | ABB MicroSCADA Pro SYS | ABB PSGuard | Catapult Software iPower SCADA | نرم‌افزار سیستم اتوماسیون توزیع | سیستم مدیریت توزیع DMS | سیستم مدیریت انرژی EMS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Milsoft DisSPatch | OSI monarch/SGP | سیستم مدیریت قطعی برق OMS | Radius NetMan | Radius Uni-View | نرم‌افزار SAP | Siemens Energy and Automation | Siemens Spectrum Power TG | Siemens Spectrum PowerCC Distribution Management | نرم‌افزار سیستم اتوماسیون پست برق | نرم‌افزار سیستم مانیتورینگ پست برق | نرم‌افزار کنترل نظارتی و گردآوری داده‌ها SCADA | Telvent Responder Outage Management System OMS | نرم‌افزار سیستم مانیتورینگ منطقه وسیع WAMS | نرم‌افزار سیستم کنترل از راه دور منطقه وسیع</t>
+          <t>ABB MicroSCADA Pro DMS | ABB MicroSCADA Pro SYS | ABB PSGuard | Catapult Software iPower SCADA | نرم‌افزار سیستم اتوماسیون توزیع | سیستم مدیریت توزیع DMS | سیستم مدیریت انرژی EMS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Milsoft DisSPatch | OSI monarch/SGP | سیستم مدیریت قطعی برق OMS | Radius NetMan | Radius Uni-View | نرم‌افزار SAP | Siemens Energy and Automation | Siemens Spectrum Power TG | Siemens Spectrum PowerCC Distribution Management | نرم‌افزار سیستم اتوماسیون پست برق | نرم‌افزار سیستم مانیتورینگ پست برق | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Telvent Responder Outage Management System OMS | نرم‌افزار سیستم مانیتورینگ منطقه وسیع WAMS | نرم‌افزار سیستم کنترل از راه دور منطقه وسیع</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | مانیتورینگ | سخن‌گفتن | نگارش | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | امنیت و ایمنی عمومی | ریاضیات | کامپیوتر و الکترونیک | مخابرات | مهندسی و فناوری | خدمات مشتریان و پرسنل | مکانیک | آموزش و پرورش | فیزیک</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مخابرات | مهندسی و فناوری | خدمات مشتری و شخصی | مکانیک | آموزش و پرورش | فیزیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | بینایی نزدیک | بیان کتبی | سازماندهی اطلاعات | وضوح گفتار | سرعت ادراکی | تشخیص گفتار | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری در بستن فضا | انعطاف‌پذیری دسته‌بندی</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | سرعت ادراکی | تشخیص گفتار | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | پیامد خطا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | اهمیت دقیق یا درست بودن | ایمیل | سلامت و ایمنی سایر کارگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | داخل ساختمان، کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | نزدیکی فیزیکی | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | برخورد با مشتریان خارجی یا عموم مردم | سطح رقابت</t>
+          <t>مکالمات تلفنی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | اهمیت دقیق یا درست بودن | ایمیل | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه قدرت زیست‌توده | تکنسین‌های پخش برنامه‌های تلویزیونی و رادیویی | نصب‌کنندگان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران الکتریکی و الکترونیکی نیروگاه، پست برق و رله | مهندسان الکترونیک، به جز کامپیوتر | اپراتورهای نیروگاه گاز | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌های نورپردازی | مهندسان مکانیک | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | تکنسین‌های پخش | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | مهندسان الکترونیک، به جز کامپیوتر | اپراتورهای واحدهای گاز | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌های نورپردازی | مهندسان مکانیک | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | سیستم‌های مانیتورینگ مستمر آلاینده‌ها CEMS | سیستم کنترل توزیع‌شده DCS | نرم‌افزار ایمیل | Emerson Ovation | نرم‌افزار سیستم مانیتورینگ میدان گاز | سیستم کنترل توزیع‌شده General Electric Mark VI DCS | سیستم کنترل یکپارچه General Electric Mark VI ICS | سیستم‌های قطع اضطراری اینترلاک | نرم‌افزار آنالیز گاز لندفیل | نرم‌افزار سیستم لندتک LFG Pro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | نرم‌افزار SAP | نرم‌افزار سیستم ابزار دقیق ایمنی SIS | اتوماسیون نیروگاه زیمنس SPPA | Siemens Teleperm | نرم‌افزار کنترل نظارتی و گردآوری داده‌ها SCADA | سیستم اطلاعات نیروگاه Teknik Segala OSI PI System | نرم‌افزار مرورگر وب | Yokogawa FAST/TOOLS</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | سیستم‌های مانیتورینگ مستمر آلاینده‌ها CEMS | سیستم کنترل توزیع‌شده DCS | نرم‌افزار ایمیل | Emerson Ovation | نرم‌افزار سیستم مانیتورینگ میدان گاز | سیستم کنترل توزیع‌شده General Electric Mark VI DCS | سیستم کنترل یکپارچه General Electric Mark VI ICS | سیستم‌های قطع اضطراری اینترلاک | نرم‌افزار تحلیل گاز محل دفن زباله | Landtec System Software LFG Pro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | نرم‌افزار SAP | نرم‌افزار سیستم ابزار دقیق ایمنی SIS | اتوماسیون نیروگاه زیمنس SPPA | Siemens Teleperm | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | سیستم اطلاعات نیروگاه Teknik Segala OSI PI System | نرم‌افزار مرورگر وب | Yokogawa FAST/TOOLS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | مانیتورینگ | گوش دادن فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | امنیت و ایمنی عمومی | زبان انگلیسی | تولید و فرآوری | شیمی | فیزیک | مهندسی و فناوری</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | شیمی | فیزیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | درک شفاهی | استدلال قیاسی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | سازماندهی اطلاعات | سرعت ادراکی | بینایی دور | چالاکی دست | توجه انتخابی | انعطاف‌پذیری در بستن فضا | درک کتبی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنوایی | زمان عکس‌العمل | دقت کنترل | چالاکی انگشتان | ثبات بازو-دست | اشتراک زمانی</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی دور | مهارت دستی | توجه انتخابی | انعطاف‌پذیری بستار | درک کتبی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | تقسیم توجه</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | ایمیل | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامد خطا | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض ارتفاعات بالا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | آزادی در تصمیم‌گیری | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | داخل ساختمان، بدون کنترل شرایط محیطی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | داخل ساختمان، کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | فضای باز، زیر سقف | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | اهمیت تکرار وظایف یکسان</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض ارتفاعات بالا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | فضای باز، زیر سقف | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه قدرت زیست‌توده | اپراتورهای سیستم و نیروگاه شیمیایی | نصب‌کنندگان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای نیروگاه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | اپراتورهای راکتور قدرت هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سر چاه | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سر چاه | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | اپراتورهای کارخانه و سامانه‌های شیمیایی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | اپراتورهای راکتور قدرت هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Distributed control system DCS | نرم‌افزار آنالیز انرژی | نرم‌افزار کنترل موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | National Instruments LabVIEW</t>
+          <t>سیستم کنترل توزیع‌شده DCS | نرم‌افزار آنالیز انرژی | نرم‌افزار کنترل موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | National Instruments LabVIEW</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | استراتژی‌های یادگیری | یادگیری فعال | سخن‌گفتن | نگارش | گوش دادن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | شیمی | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | آموزش و پرورش | کامپیوتر و الکترونیک</t>
+          <t>مکانیک | شیمی | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | حساسیت به مشکلات | سازماندهی اطلاعات | درک کتبی | استدلال قیاسی | سرعت ادراکی | هماهنگی چند عضو | زمان عکس‌العمل | تشخیص رنگ بصری | بینایی دور | کنترل سرعت | ثبات بازو-دست | توجه انتخابی | تجسم | استدلال استقرایی | توجه شنوایی | حساسیت شنوایی | چالاکی دست | اشتراک زمانی | بیان کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | استدلال قیاسی | سرعت ادراکی | هماهنگی چند عضو | زمان عکس‌العمل | تشخیص رنگ بصری | بینایی دور | کنترل نرخ | ثبات دست و بازو | توجه انتخابی | تجسم | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | مهارت دستی | تقسیم توجه | بیان کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض ارتفاعات بالا | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | ارتباط با دیگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | پیامدهای کاری و نتایج سایر کارگران | داخل ساختمان، کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت دقیق یا درست بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | داخل ساختمان، بدون کنترل شرایط محیطی | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | سرعت تعیین شده توسط سرعت تجهیزات | نامه‌ها و یادداشت‌های کتبی | صرف زمان به صورت نشسته</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض ارتفاعات بالا | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | ارتباط با دیگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی | سرعت تعیین‌شده توسط سرعت تجهیزات | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مدیران نیروگاه قدرت زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و نیروگاه شیمیایی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای نیروگاه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سر چاه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سر چاه | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | سیستم کنترل توزیع‌شده DCS | IBM Lotus Notes | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار کنترل نظارتی و گردآوری داده‌ها SCADA | نرم‌افزار مرورگر وب</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | سیستم کنترل توزیع‌شده DCS | IBM Lotus Notes | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | درک مطلب | گوش دادن فعال | سخن‌گفتن | یادگیری فعال | ریاضیات | نگارش</t>
+          <t>تفکر انتقادی | نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | امنیت و ایمنی عمومی | ریاضیات | مهندسی و فناوری | آموزش و پرورش | طراحی | زبان انگلیسی | کامپیوتر و الکترونیک | فیزیک | ساختمان و ساخت‌وساز | مدیریت و امور اداری | تولید و فرآوری | قانون و دولت | حمل‌ونقل | مخابرات | امور اداری | خدمات مشتریان و پرسنل</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | آموزش و پرورش | طراحی | زبان انگلیسی | رایانه و الکترونیک | فیزیک | ساختمان و ساخت‌وساز | مدیریت و اداره | تولید و فرآوری | قانون و دولت | حمل و نقل | مخابرات | اداری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مشکلات | سازماندهی اطلاعات | دقت کنترل | درک شفاهی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | بیان شفاهی | تشخیص گفتار | تجسم | سرعت ادراکی | درک کتبی | بینایی دور | وضوح گفتار | انعطاف‌پذیری بدنی | هماهنگی چند عضو | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | انعطاف‌پذیری در بستن فضا | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | تعادل کلی بدن | قدرت تنه</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دقت کنترل | درک شفاهی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | بیان شفاهی | تشخیص گفتار | تجسم | سرعت ادراکی | درک کتبی | بینایی دور | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | تعادل کلی بدن | قدرت تنه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | داخل ساختمان، بدون کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران | داخل ساختمان, کنترل شرایط محیطی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | محیط داخلی، بدون کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه قدرت زیست‌توده | نصب‌کنندگان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران الکتریکی و الکترونیکی نیروگاه، پست برق و رله | اپراتورهای نیروگاه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | مدیران تولید برق‌آبی | کارگران نگهداری و تعمیرات، عمومی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان کشتی | نصب‌کنندگان سیستم‌های خورشیدی فتوولتائیک | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سر چاه | مهندسان انرژی باد | تکنسین‌های خدمات توربین بادی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | مدیران تولید برق‌آبی | کارگران نگهداری و تعمیرات عمومی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان کشتی | نصابان سیستم‌های فتوولتائیک خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی | مهندسان انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم مدیریت ساختمان | سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار گرافیکی | صفحات سرور فعال مایکروسافت ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | نرم‌افزار SAP | نرم‌افزار آماری | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار سیستم مدیریت ساختمان | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار گرافیکی | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | نرم‌افزار SAP | نرم‌افزار آماری | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | مانیتورینگ | سخن‌گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | شیمی | امنیت و ایمنی عمومی | فیزیک | مهندسی و فناوری | زبان انگلیسی | کامپیوتر و الکترونیک | ریاضیات | تولید و فرآوری</t>
+          <t>مکانیک | شیمی | ایمنی و امنیت عمومی | فیزیک | مهندسی و فناوری | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مشکلات | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | سرعت ادراکی | توجه شنوایی | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | تشخیص گفتار | بینایی دور | بیان کتبی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه شنیداری | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | تشخیص گفتار | بینایی دور | بیان کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | ایمیل | داخل ساختمان، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | اهمیت دقیق یا درست بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان، کنترل شرایط محیطی | فشار زمانی | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ایمیل | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | دیگ‌سازان | نصب‌کنندگان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران الکتریکی و الکترونیکی نیروگاه، پست برق و رله | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای نیروگاه گاز | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصب‌کنندگان گرمایش، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و تعمیرات، عمومی | مهندسان مکانیک | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | لوله‌کشان، لوله‌کشان صنعتی و بخارکاران | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سر چاه | مهندسان کشتی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | دیگ‌سازان | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و تعمیرات عمومی | مهندسان مکانیک | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | مهندسان کشتی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0090_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0090_fa.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>مدل‌سازان چوب (Patternmakers, Wood)</t>
+          <t>الگوسازان چوب (Patternmakers, Wood)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | Mastercam computer-aided design and manufacturing software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook</t>
+          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | ریاضیات | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | ریاضیات | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | طراحی | مهندسی و فناوری | مکانیک | ساخت و ساز | مدیریت و امور اداری | تولید و فرآوری | خدمات مشتریان و خدمات فردی</t>
+          <t>ریاضیات | طراحی | مهندسی و فناوری | مکانیک | ساختمان و ساخت‌وساز | مدیریت و اداره | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت کنترل | ثبات دست و بازو | دید نزدیک | زمان واکنش | چابکی انگشتان | مرتب‌سازی اطلاعات | تجسم فضایی | استحکام ایستا | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | سرعت ادراک | استدلال ریاضی | بیان شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | ادراک عمق | قدرت تنه</t>
+          <t>مهارت دستی | دقت کنترل | ثبات دست و بازو | بینایی نزدیک | زمان عکس‌العمل | مهارت انگشتان | ترتیب‌دهی اطلاعات | تجسم | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | سرعت ادراکی | استدلال ریاضی | بیان شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | درک عمق | قدرت تنه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان | کابینت‌سازان و نجاران کارگاهی | نجاران | حکاکان و قلم‌زنان | الگوبران پارچه و پوشاک | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | کارگران پرداخت و سنگ‌زنی دستی | خط‌کشان فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، متصدیان و اپراتورهای فرز و رنده فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان و شکل‌دهندگان غیرفلزی | مدل‌سازان فلز و پلاستیک | ورق‌کاران فلزی | سنگ‌تراشان و حجارهای صنعتی | سازندگان و مونتاژکاران سازه‌های فلزی | ابزارسازان و قالب‌سازان | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌های چوب‌بری به‌جز اره</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | حکاکان و اسیدکاران | الگوسازان پارچه و پوشاک | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | الگوسازان فلز و پلاستیک | کارگران ورق‌کاری فلزی | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار انبارداری خودکار | Computerized numerical control CNC software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word</t>
+          <t>Adobe Acrobat | نرم‌افزار خودکار موجودی | Computerized numerical control CNC software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | چابکی دستی | ثبات دست و بازو | کنترل سرعت | زمان واکنش | حساسیت به مسئله | چابکی انگشتان | استقامت بدنی | قدرت تنه | هماهنگی چند اندام | توجه انتخابی | ادراک عمق | دید دور | استحکام ایستا | استدلال استقرایی | استدلال قیاسی</t>
+          <t>دقت کنترل | بینایی نزدیک | مهارت دستی | ثبات دست و بازو | کنترل نرخ | زمان عکس‌العمل | حساسیت به مسئله | مهارت انگشتان | استقامت | قدرت تنه | هماهنگی چند عضو | توجه انتخابی | درک عمق | بینایی دور | قدرت ایستا | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و متصدیان دستگاه‌های سنگ‌شکن و پرداخت | برشکاران دستی | تنظیم‌کنندگان و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان و متصدیان دستگاه‌های برش و پرس فلز و پلاستیک | تنظیم‌کنندگان و متصدیان ماشین‌آلات دریل و حفاری فلز و پلاستیک | تنظیم‌کنندگان و متصدیان دستگاه‌های آهنگری فلز و پلاستیک | کارگران پرداخت و سنگ‌زنی دستی | تنظیم‌کنندگان و متصدیان ماشین‌آلات سنگ‌زنی و پولیش فلز و پلاستیک | تنظیم‌کنندگان و متصدیان تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان خطوط تولید ماشین‌آلات | تنظیم‌کنندگان، متصدیان و اپراتورهای فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان و متصدیان دستگاه‌های چندکاره فلز و پلاستیک | تنظیم‌کنندگان و متصدیان ماشین‌های تولید فرآورده‌های کاغذی | تنظیم‌کنندگان و متصدیان ماشین‌های نورد فلز و پلاستیک | چرخ‌کاران و دوزندگان صنعتی | اپراتورهای ماشین‌های کفاشی | تنظیم‌کنندگان و متصدیان ماشین‌های برش منسوجات | سنگ‌زن‌ها و تیزکاران ابزار | ابزارسازان و قالب‌سازان | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌های چوب‌بری به‌جز اره</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | زمان واکنش | دقت کنترل | چابکی دستی | درک شفاهی | حساسیت به مسئله | هماهنگی چند اندام | استحکام ایستا | قدرت تنه | توجه شنوایی | دید دور | چابکی انگشتان | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | سرعت ادراک | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری بدنی | قدرت پویا | کنترل سرعت | انعطاف‌پذیری شناختی</t>
+          <t>بینایی نزدیک | زمان عکس‌العمل | دقت کنترل | مهارت دستی | درک شفاهی | حساسیت به مسئله | هماهنگی چند عضو | قدرت ایستا | قدرت تنه | توجه شنیداری | بینایی دور | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | تجسم | سرعت ادراکی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت پویا | کنترل نرخ | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و متصدیان دستگاه‌های سنگ‌شکن و پرداخت | برشکاران دستی | تنظیم‌کنندگان و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان و متصدیان دستگاه‌های برش و پرس فلز و پلاستیک | تنظیم‌کنندگان و متصدیان ماشین‌آلات دریل و حفاری فلز و پلاستیک | تنظیم‌کنندگان و متصدیان دستگاه‌های آهنگری فلز و پلاستیک | کارگران پرداخت و سنگ‌زنی دستی | تنظیم‌کنندگان و متصدیان ماشین‌آلات سنگ‌زنی و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و متصدیان تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان خطوط تولید ماشین‌آلات | تنظیم‌کنندگان، متصدیان و اپراتورهای فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان و متصدیان دستگاه‌های چندکاره فلز و پلاستیک | تنظیم‌کنندگان و متصدیان ماشین‌های تولید فرآورده‌های کاغذی | تنظیم‌کنندگان و متصدیان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | اپراتورهای ماشین‌های کفاشی | تنظیم‌کنندگان و متصدیان ماشین‌های برش منسوجات | سنگ‌زن‌ها و تیزکاران ابزار | ابزارسازان و قالب‌سازان</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | ساخت و ساز | شیمی</t>
+          <t>تولید و فرآوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | ساختمان و ساخت‌وساز | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چند اندام | دقت کنترل | استحکام ایستا | قدرت تنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | رنگ‌کاران و پرداخت‌کاران مبلمان | مدل‌سازان چوب | مدل‌سازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌های چوب‌بری به‌جز اره | نجاران | کمک‌نجاران | رویه‌کوبان مبل | سنباده‌زنان و نصابان کف‌پوش چوبی | رنگ‌کاران و تزیین‌کاران صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های پوشش‌دهی، رنگ‌رزی و اسپری | بازرسان، آزمون‌گران، درجه‌بندان و توزین‌کنندگان | اپراتورهای ابزارهای کنترل عددی رایانه‌ای (CNC) | سرپرستان رده‌اول کارگران تولید و عملیات | کمک‌کارگران تولید | سایر کارگران تولیدی | درجه‌بندان و ارزیابان الوار | اپراتورهای ماشین‌های چسب‌زنی و اتصال | قالب‌ریزان و شکل‌دهندگان غیرفلزی</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | مدل‌سازان چوب | الگوسازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره | نجاران و درودگران | کمک‌نجاران | رویه‌کوبان و مبل‌کوبان | ساب‌زنان و پرداخت‌کاران کف | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | سرپرستان رده اول کارگران تولید و عملیات | کمک‌کارگران خطوط تولید | سایر کارگران خطوط تولید | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | سرعت ادراک | دید نزدیک | استدلال قیاسی | استدلال استقرایی | بیان کتبی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری شناختی | تشخیص گفتار | دید دور | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | ابتکار و نوآوری | روانی ایده‌ها | تقسیم توجه | توجه شنوایی | حساسیت شنوایی | تشخیص رنگ</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | بیان کتبی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار | بینایی دور | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | اصالت | روانی ایده‌ها | تقسیم توجه | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | متصدیان پالایشگاه و فرآیندهای شیمیایی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی صنعتی | تعمیرکاران ترانسفورماتور و رله نیروگاهی و پست‌های برق | متصدیان تأسیسات گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برقابی | مدیران تولید نیروگاه برقابی | مهندسان هسته‌ای | تکنسین‌های پایش پرتوی هسته‌ای | تکنسین‌های هسته‌ای | متصدیان پمپاژ و تجهیزات پالایشگاه نفت | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | متصدیان تصفیه‌خانه و شبکه‌های آب و فاضلاب</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | تکنسین‌های هسته‌ای | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مخابرات و ارتباطات | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | مکانیک | آموزش و تدریس | فیزیک</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مخابرات | مهندسی و فناوری | خدمات مشتری و شخصی | مکانیک | آموزش و پرورش | فیزیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | وضوح گفتار | سرعت ادراک | تشخیص گفتار | دید دور | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری شناختی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | سرعت ادراکی | تشخیص گفتار | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | تکنسین‌های پخش و ارتباطات رادیویی | نصابان و تعمیرکاران کنترل‌ها و شیرهای صنعتی | مهندسان برق | کاردان‌ها و تکنسین‌های فنی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی صنعتی | تعمیرکاران ترانسفورماتور و رله نیروگاهی و پست‌های برق | مهندسان الکترونیک به‌جز رایانه | متصدیان تأسیسات گاز | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برقابی | تکنسین‌های نور و روشنایی صنعتی | مهندسان مکانیک | متصدیان پمپاژ و تجهیزات پالایشگاه نفت | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | تکنسین‌های پخش و اتاق فرمان | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مهندسان الکترونیک، به‌جز کامپیوتر | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | تکنسین‌های نورپردازی | مهندسان مکانیک | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | دید نزدیک | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | سرعت ادراک | دید دور | چابکی دستی | توجه انتخابی | انعطاف‌پذیری شناختی | درک کتبی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنوایی | زمان واکنش | دقت کنترل | چابکی انگشتان | ثبات دست و بازو | تقسیم توجه</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی دور | مهارت دستی | توجه انتخابی | انعطاف‌پذیری بستار | درک کتبی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | تقسیم توجه</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | متصدیان پالایشگاه و فرآیندهای شیمیایی | نصابان و تعمیرکاران کنترل‌ها و شیرهای صنعتی | اپراتورهای ایستگاه تقویت فشار و کمپرسور گاز | متصدیان تأسیسات گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برقابی | مدیران تولید نیروگاه برقابی | اپراتورهای رآکتور نیروگاه هسته‌ای | تکنسین‌های هسته‌ای | متصدیان پمپاژ و تجهیزات پالایشگاه نفت | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای پمپ‌های صنعتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | متصدیان تصفیه‌خانه و شبکه‌های آب و فاضلاب | اپراتورهای سرچاهی نفت و گاز | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | اپراتورهای رآکتور نیروگاه هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | سخن گفتن | نگارش | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | شیمی | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | آموزش و تدریس | رایانه و الکترونیک</t>
+          <t>مکانیک | شیمی | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی | استدلال قیاسی | سرعت ادراک | هماهنگی چند اندام | زمان واکنش | تشخیص رنگ | دید دور | کنترل سرعت | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | استدلال استقرایی | توجه شنوایی | حساسیت شنوایی | چابکی دستی | تقسیم توجه | بیان کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | استدلال قیاسی | سرعت ادراکی | هماهنگی چند عضو | زمان عکس‌العمل | تشخیص رنگ بصری | بینایی دور | کنترل نرخ | ثبات دست و بازو | توجه انتخابی | تجسم | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | مهارت دستی | تقسیم توجه | بیان کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری بیودیزل | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | متصدیان و اپراتورهای تجهیزات شیمیایی | متصدیان پالایشگاه و فرآیندهای شیمیایی | اپراتورهای ایستگاه تقویت فشار و کمپرسور گاز | متصدیان تأسیسات گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برقابی | متصدیان پمپاژ و تجهیزات پالایشگاه نفت | اپراتورهای نیروگاه برق | اپراتورهای پمپ‌های صنعتی | متصدیان دستگاه‌های تصفیه، فیلتراسیون و تقطیر | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | متصدیان تصفیه‌خانه و شبکه‌های آب و فاضلاب | اپراتورهای سرچاهی نفت و گاز | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش</t>
+          <t>تفکر انتقادی | نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | آموزش و تدریس | طراحی | زبان انگلیسی | رایانه و الکترونیک | فیزیک | ساخت و ساز | مدیریت و امور اداری | تولید و فرآوری | حقوق و مقررات دولتی | ترابری و حمل‌ونقل | مخابرات و ارتباطات | امور دفتری و اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | آموزش و پرورش | طراحی | زبان انگلیسی | رایانه و الکترونیک | فیزیک | ساختمان و ساخت‌وساز | مدیریت و اداره | تولید و فرآوری | قانون و دولت | حمل و نقل | مخابرات | اداری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | دقت کنترل | درک شفاهی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | بیان شفاهی | تشخیص گفتار | تجسم فضایی | سرعت ادراک | درک کتبی | دید دور | وضوح گفتار | انعطاف‌پذیری بدنی | هماهنگی چند اندام | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | انعطاف‌پذیری شناختی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ | تعادل کلی بدن | قدرت تنه</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دقت کنترل | درک شفاهی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | بیان شفاهی | تشخیص گفتار | تجسم | سرعت ادراکی | درک کتبی | بینایی دور | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | تعادل کلی بدن | قدرت تنه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | نصابان و تعمیرکاران کنترل‌ها و شیرهای صنعتی | تعمیرکاران ترانسفورماتور و رله نیروگاهی و پست‌های برق | متصدیان تأسیسات گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | مدیران تولید نیروگاه برقابی | کارگران عمومی تعمیر و نگهداری | متصدیان پمپاژ و تجهیزات پالایشگاه نفت | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق | مهندسان کشتی | نصابان پنل‌های خورشیدی فتوولتائیک | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | متصدیان تصفیه‌خانه و شبکه‌های آب و فاضلاب | اپراتورهای سرچاهی نفت و گاز | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | مدیران تولید نیروگاه‌های برق‌آبی | کارگران عمومی تعمیرات و نگهداری تاسیسات | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان فنی کشتی | نصابان سیستم‌های خورشیدی فتوولتائیک | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | سرعت ادراک | توجه شنوایی | زمان واکنش | هماهنگی چند اندام | دقت کنترل | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | تشخیص گفتار | دید دور | بیان کتبی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه شنیداری | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | تشخیص گفتار | بینایی دور | بیان کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | دیگ‌سازان | نصابان و تعمیرکاران کنترل‌ها و شیرهای صنعتی | تعمیرکاران ترانسفورماتور و رله نیروگاهی و پست‌های برق | مونتاژکاران موتور و ماشین‌آلات صنعتی | اپراتورهای ایستگاه تقویت فشار و کمپرسور گاز | متصدیان تأسیسات گاز | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های سرمایش، گرمایش و تهویه مطبوع | تکنسین‌های نیروگاه‌های برقابی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیر و نگهداری | مهندسان مکانیک | متصدیان پمپاژ و تجهیزات پالایشگاه نفت | لوله‌کشان و تأسیسات‌کاران صنعتی | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ‌های صنعتی | مهندسان کشتی | متصدیان تصفیه‌خانه و شبکه‌های آب و فاضلاب</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | دیگ‌سازان و مخزن‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های سامانه‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برقابی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان مکانیک | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | مهندسان فنی کشتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
